--- a/output/graficos_educacion_tasas/plot_regional_e_matricula_a_provincial_2022_biobio.xlsx
+++ b/output/graficos_educacion_tasas/plot_regional_e_matricula_a_provincial_2022_biobio.xlsx
@@ -60,7 +60,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 17:42</t>
+    <t xml:space="preserve">2026-09-09 20:46</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_educacion_tasas/plot_regional_e_matricula_a_provincial_2022_biobio.xlsx
+++ b/output/graficos_educacion_tasas/plot_regional_e_matricula_a_provincial_2022_biobio.xlsx
@@ -8,12 +8,13 @@
   <sheets>
     <sheet name="Provincial" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Metadata" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Provincial_sexo" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Tramo_etario" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Tramo_etario_nacional" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Media_nacional" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Provincial_sexo" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Tramo_etario" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Tramo_etario_nacional" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Tramo_etario_nacional'!$A$1:$C$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Tramo_etario_nacional'!$A$1:$C$8</definedName>
   </definedNames>
 </workbook>
 </file>
@@ -60,7 +61,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 20:46</t>
+    <t xml:space="preserve">2026-09-18 10:37</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -87,6 +88,9 @@
     <t xml:space="preserve">Año</t>
   </si>
   <si>
+    <t xml:space="preserve">Media nacional (%)</t>
+  </si>
+  <si>
     <t xml:space="preserve">Mujeres (%)</t>
   </si>
   <si>
@@ -118,9 +122,6 @@
   </si>
   <si>
     <t xml:space="preserve">16 a 17 años</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Media nacional (%)</t>
   </si>
 </sst>
 </file>
@@ -717,6 +718,62 @@
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
     <col min="1" max="1" width="12.71" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="20.71" hidden="0" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="2" t="n">
+        <v>58.44</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" s="2" t="n">
+        <v>94.28</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>86.91</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>43.38</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:B5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+  <cols>
+    <col min="1" max="1" width="12.71" hidden="0" customWidth="1"/>
     <col min="2" max="2" width="12.71" hidden="0" customWidth="1"/>
     <col min="3" max="3" width="13.71" hidden="0" customWidth="1"/>
     <col min="4" max="4" width="13.71" hidden="0" customWidth="1"/>
@@ -730,10 +787,10 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="2">
@@ -911,7 +968,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
@@ -930,304 +987,304 @@
         <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>3</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>28.88</v>
+        <v>23.9</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>3</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>63.42</v>
+        <v>59.74</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>3</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>95.52</v>
+        <v>95.5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>3</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>20.34</v>
+        <v>28.88</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>3</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>58.07</v>
+        <v>63.42</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>3</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>95.77</v>
+        <v>95.52</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>3</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>23.9</v>
+        <v>20.34</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>3</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>59.74</v>
+        <v>58.07</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>3</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>95.5</v>
+        <v>95.77</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>95.41</v>
+        <v>94.4</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>98.56</v>
+        <v>96.78</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>95.31</v>
+        <v>95.41</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>98.28</v>
+        <v>98.56</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>94.4</v>
+        <v>95.31</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>96.78</v>
+        <v>98.28</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>8</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D17" s="2" t="n">
-        <v>89.03</v>
+        <v>89.72</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>8</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D18" s="2" t="n">
-        <v>86.07</v>
+        <v>88.01</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>8</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D19" s="2" t="n">
-        <v>90.5</v>
+        <v>89.03</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>8</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D20" s="2" t="n">
-        <v>88.8</v>
+        <v>86.07</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>8</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D21" s="2" t="n">
-        <v>89.72</v>
+        <v>90.5</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>8</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D22" s="2" t="n">
-        <v>88.01</v>
+        <v>88.8</v>
       </c>
     </row>
   </sheetData>
@@ -1237,7 +1294,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
@@ -1252,10 +1309,10 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
     </row>
     <row r="2">
@@ -1263,7 +1320,7 @@
         <v>3</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C2" s="2" t="n">
         <v>91.65</v>
@@ -1274,7 +1331,7 @@
         <v>3</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C3" s="2" t="n">
         <v>53.07</v>
@@ -1285,7 +1342,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C4" s="2" t="n">
         <v>22.46</v>
@@ -1296,7 +1353,7 @@
         <v>7</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C5" s="2" t="n">
         <v>93.67</v>
@@ -1307,7 +1364,7 @@
         <v>7</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C6" s="2" t="n">
         <v>94.91</v>
@@ -1318,7 +1375,7 @@
         <v>8</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C7" s="2" t="n">
         <v>87.26</v>
@@ -1329,7 +1386,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C8" s="2" t="n">
         <v>86.58</v>

--- a/output/graficos_educacion_tasas/plot_regional_e_matricula_a_provincial_2022_biobio.xlsx
+++ b/output/graficos_educacion_tasas/plot_regional_e_matricula_a_provincial_2022_biobio.xlsx
@@ -61,7 +61,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 10:37</t>
+    <t xml:space="preserve">2026-09-23 16:21</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_educacion_tasas/plot_regional_e_matricula_a_provincial_2022_biobio.xlsx
+++ b/output/graficos_educacion_tasas/plot_regional_e_matricula_a_provincial_2022_biobio.xlsx
@@ -61,7 +61,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-23 16:21</t>
+    <t xml:space="preserve">2026-10-05 05:58</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
